--- a/data/processed/modeling/encuestas_y_sentimiento_mensual_unificado.xlsx
+++ b/data/processed/modeling/encuestas_y_sentimiento_mensual_unificado.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mensual_unificado" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'mensual_unificado'!$A$1:$T$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'mensual_unificado'!$A$1:$T$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T19"/>
+  <dimension ref="A1:T20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1773,39 +1773,99 @@
       <c r="J19" s="3" t="inlineStr"/>
       <c r="K19" s="3" t="inlineStr"/>
       <c r="L19" t="n">
+        <v>4</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="n">
+        <v>0.7797959572845157</v>
+      </c>
+      <c r="P19" s="5" t="n">
+        <v>0.2004993413595564</v>
+      </c>
+      <c r="Q19" s="5" t="n">
+        <v>-0.2193587134390587</v>
+      </c>
+      <c r="R19" s="5" t="n">
+        <v>0.1041126033256538</v>
+      </c>
+      <c r="S19" s="5" t="n">
+        <v>0.1240178669425632</v>
+      </c>
+      <c r="T19" s="5" t="n">
+        <v>0.1140652351341085</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B20" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ABRIL</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr"/>
+      <c r="I20" s="4" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2026-W10</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2026-W10</t>
-        </is>
-      </c>
-      <c r="O19" s="5" t="n">
-        <v>0.9565217391304348</v>
-      </c>
-      <c r="P19" s="5" t="n">
-        <v>0.08641975308641975</v>
-      </c>
-      <c r="Q19" s="5" t="n">
-        <v>-0.08942425479787669</v>
-      </c>
-      <c r="R19" s="5" t="n">
-        <v>0.2100585882774014</v>
-      </c>
-      <c r="S19" s="5" t="n">
-        <v>0.1278439869989166</v>
-      </c>
-      <c r="T19" s="5" t="n">
-        <v>0.168951287638159</v>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="n">
+        <v>0.7878787878787878</v>
+      </c>
+      <c r="P20" s="5" t="n">
+        <v>0.286624203821656</v>
+      </c>
+      <c r="Q20" s="5" t="n">
+        <v>-0.262483994878361</v>
+      </c>
+      <c r="R20" s="5" t="n">
+        <v>0.09355609798026393</v>
+      </c>
+      <c r="S20" s="5" t="n">
+        <v>0.1218498311249675</v>
+      </c>
+      <c r="T20" s="5" t="n">
+        <v>0.1077029645526157</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T19"/>
+  <autoFilter ref="A1:T20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/processed/modeling/encuestas_y_sentimiento_mensual_unificado.xlsx
+++ b/data/processed/modeling/encuestas_y_sentimiento_mensual_unificado.xlsx
@@ -24,16 +24,13 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -53,7 +50,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -61,21 +58,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1786,7 +1775,7 @@
         </is>
       </c>
       <c r="O19" s="5" t="n">
-        <v>0.7797959572845157</v>
+        <v>0.719033495515911</v>
       </c>
       <c r="P19" s="5" t="n">
         <v>0.2004993413595564</v>
@@ -1795,13 +1784,13 @@
         <v>-0.2193587134390587</v>
       </c>
       <c r="R19" s="5" t="n">
-        <v>0.1041126033256538</v>
+        <v>0.08823089893224371</v>
       </c>
       <c r="S19" s="5" t="n">
         <v>0.1240178669425632</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>0.1140652351341085</v>
+        <v>0.1061243829374034</v>
       </c>
     </row>
     <row r="20">
@@ -1833,7 +1822,7 @@
       <c r="J20" s="3" t="inlineStr"/>
       <c r="K20" s="3" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1842,26 +1831,26 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-W14</t>
+          <t>2026-W18</t>
         </is>
       </c>
       <c r="O20" s="5" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.6747486526041067</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>0.286624203821656</v>
+        <v>0.1991694834161488</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>-0.262483994878361</v>
+        <v>-0.2270380117648613</v>
       </c>
       <c r="R20" s="5" t="n">
-        <v>0.09355609798026393</v>
+        <v>0.07192631108934171</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>0.1218498311249675</v>
+        <v>0.09187000944613169</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>0.1077029645526157</v>
+        <v>0.08189816026773669</v>
       </c>
     </row>
   </sheetData>
